--- a/tests/TC-13/results/teacher_timetables_even.xlsx
+++ b/tests/TC-13/results/teacher_timetables_even.xlsx
@@ -639,21 +639,15 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>MA163 TUT
 (CSE_4_B)
-Room: 104</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>MA163 TUT
-(CSE_4_B)
-Room: 104</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr"/>
+Room: 117</t>
+        </is>
+      </c>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
@@ -926,30 +920,36 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>CS162 TUT
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>CS162 TUT
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CS162 TUT
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 118</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 118</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 118</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 118</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
@@ -971,34 +971,10 @@
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
@@ -1022,10 +998,34 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 118</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 118</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 118</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 118</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -1050,28 +1050,34 @@
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>CS162 TUT
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>CS162 TUT
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>CS162 TUT
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
@@ -1305,8 +1311,20 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>CS151 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>CS151 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
@@ -1329,20 +1347,8 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>CS151 TUT
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>CS151 TUT
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
@@ -1368,8 +1374,20 @@
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>CS151 TUT
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>CS151 TUT
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
@@ -1401,27 +1419,9 @@
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>CS151 LEC
-(CSE_4_B)
-Room: 106</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>CS151 LEC
-(CSE_4_B)
-Room: 106</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>CS151 LEC
-(CSE_4_B)
-Room: 106</t>
-        </is>
-      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
@@ -1614,8 +1614,20 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>DS151 LEC
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>DS151 LEC
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
@@ -1654,29 +1666,17 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 117</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 117</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 117</t>
-        </is>
-      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>DS151 TUT
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
@@ -1686,8 +1686,20 @@
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>DS151 LEC
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>DS151 LEC
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
@@ -1699,27 +1711,9 @@
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 117</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 117</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 117</t>
-        </is>
-      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
@@ -1731,13 +1725,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>DS151 TUT
-(CSE_4_B)
-Room: 120</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
@@ -1918,8 +1906,20 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1948,32 +1948,62 @@
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -1985,45 +2015,51 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
@@ -2035,54 +2071,30 @@
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
@@ -2100,52 +2112,16 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -2319,40 +2295,34 @@
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_4_B)
+Room: 107</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_4_B)
+Room: 107</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_4_B)
+Room: 107</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
@@ -2380,27 +2350,9 @@
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -2476,9 +2428,27 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_4_B)
+Room: 107</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_4_B)
+Room: 107</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_4_B)
+Room: 107</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2657,27 +2627,9 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="O3" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
@@ -2728,20 +2680,8 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -2771,9 +2711,27 @@
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
     </row>
@@ -2785,10 +2743,34 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
@@ -3026,8 +3008,20 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>DA151 TUT
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>DA151 TUT
+(CSE_4_B)
+Room: 115</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
@@ -3036,13 +3030,7 @@
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>DA151 TUT
-(CSE_4_B)
-Room: 110</t>
-        </is>
-      </c>
+      <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
@@ -3260,13 +3248,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>NEW TUT
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
+      <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
@@ -3281,15 +3263,21 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>NEW TUT
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>HS159 TUT
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>HS159 TUT
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
@@ -3306,20 +3294,8 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>EC155 TUT
-(CSE_4_B)
-Room: 119</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>EC155 TUT
-(CSE_4_B)
-Room: 119</t>
-        </is>
-      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr"/>
@@ -3382,13 +3358,7 @@
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>HS159 TUT
-(CSE_4_B)
-Room: 108</t>
-        </is>
-      </c>
+      <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
@@ -3405,16 +3375,40 @@
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>NEW TUT
+(CSE_4_B)
+Room: 111</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>NEW TUT
+(CSE_4_B)
+Room: 111</t>
+        </is>
+      </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>EC155 TUT
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>EC155 TUT
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>

--- a/tests/TC-13/results/teacher_timetables_even.xlsx
+++ b/tests/TC-13/results/teacher_timetables_even.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dr. Anand Barangi" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dr. Dibyajyoti Guha" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Dr. Rajendra H" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dr. Shrishendu Layek" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Dr. Suvadip Hazra" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Dr. Swagatika Sahoo" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Dr. Vivekraj" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Prof. S R M Prasanna" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="TBD" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Dr. Dibyajyoti Guha" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dr. Rajendra H" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dr. Shrishendu Layek" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dr. Suvadip Hazra" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dr. Swagatika Sahoo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dr. Vivekraj" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Prof. S R M Prasanna" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TBD_EC155" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TBD_HS159" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dr. Anand Barangi  Weekly Timetable</t>
+          <t>Dr. Dibyajyoti Guha  Weekly Timetable</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>CS162 TUT
+(CSE_4_B)
+Room: 107</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
@@ -641,13 +647,7 @@
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>MA163 TUT
-(CSE_4_B)
-Room: 117</t>
-        </is>
-      </c>
+      <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
@@ -687,10 +687,34 @@
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 105</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 105</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 105</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 105</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
@@ -725,9 +749,27 @@
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 105</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 105</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_4_B)
+Room: 105</t>
+        </is>
+      </c>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
     </row>
@@ -801,7 +843,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dr. Dibyajyoti Guha  Weekly Timetable</t>
+          <t>Dr. Rajendra H  Weekly Timetable</t>
         </is>
       </c>
     </row>
@@ -922,36 +964,24 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 118</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 118</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 118</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 118</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>CS151 TUT
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>CS151 TUT
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -973,10 +1003,34 @@
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>CS151 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>CS151 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>CS151 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>CS151 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
@@ -998,41 +1052,29 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 118</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 118</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 118</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 118</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>CS151 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>CS151 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -1050,27 +1092,9 @@
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>CS162 TUT
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>CS162 TUT
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>CS162 TUT
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -1156,7 +1180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dr. Rajendra H  Weekly Timetable</t>
+          <t>Dr. Shrishendu Layek  Weekly Timetable</t>
         </is>
       </c>
     </row>
@@ -1284,8 +1308,20 @@
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>DS151 LEC
+(CSE_4_B)
+Room: 116</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>DS151 LEC
+(CSE_4_B)
+Room: 116</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -1313,16 +1349,16 @@
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>CS151 LEC
-(CSE_4_B)
-Room: 119</t>
+          <t>DS151 LEC
+(CSE_4_B)
+Room: 116</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>CS151 LEC
-(CSE_4_B)
-Room: 119</t>
+          <t>DS151 LEC
+(CSE_4_B)
+Room: 116</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr"/>
@@ -1376,16 +1412,16 @@
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>CS151 TUT
-(CSE_4_B)
-Room: 119</t>
+          <t>DS151 TUT
+(CSE_4_B)
+Room: 117</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>CS151 TUT
-(CSE_4_B)
-Room: 119</t>
+          <t>DS151 TUT
+(CSE_4_B)
+Room: 117</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr"/>
@@ -1469,7 +1505,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dr. Shrishendu Layek  Weekly Timetable</t>
+          <t>Dr. Suvadip Hazra  Weekly Timetable</t>
         </is>
       </c>
     </row>
@@ -1614,20 +1650,8 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
@@ -1640,9 +1664,27 @@
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -1653,8 +1695,20 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1667,16 +1721,28 @@
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>DS151 TUT
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
@@ -1686,24 +1752,36 @@
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
@@ -1727,16 +1805,52 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>CS165/CS201 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -1788,7 +1902,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra  Weekly Timetable</t>
+          <t>Dr. Swagatika Sahoo  Weekly Timetable</t>
         </is>
       </c>
     </row>
@@ -1906,20 +2020,8 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1932,9 +2034,27 @@
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -1945,37 +2065,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
@@ -1983,27 +2091,9 @@
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -2024,42 +2114,12 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
@@ -2081,20 +2141,8 @@
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 109</t>
-        </is>
-      </c>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
@@ -2173,7 +2221,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dr. Swagatika Sahoo  Weekly Timetable</t>
+          <t>Dr. Vivekraj  Weekly Timetable</t>
         </is>
       </c>
     </row>
@@ -2292,37 +2340,43 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
-      <c r="O3" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
@@ -2400,8 +2454,20 @@
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
@@ -2428,27 +2494,9 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2498,7 +2546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj  Weekly Timetable</t>
+          <t>Prof. S R M Prasanna  Weekly Timetable</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2745,13 @@
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>DA151 TUT
+(CSE_4_B)
+Room: 120</t>
+        </is>
+      </c>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
@@ -2711,27 +2765,9 @@
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
-      <c r="S6" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
     </row>
@@ -2743,34 +2779,10 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
@@ -2780,9 +2792,27 @@
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>DA151 LEC
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>DA151 LEC
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>DA151 LEC
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
@@ -2829,7 +2859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Prof. S R M Prasanna  Weekly Timetable</t>
+          <t>TBD_EC155  Weekly Timetable</t>
         </is>
       </c>
     </row>
@@ -3008,20 +3038,8 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>DA151 TUT
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>DA151 TUT
-(CSE_4_B)
-Room: 115</t>
-        </is>
-      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
@@ -3067,7 +3085,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>EC155 TUT
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
@@ -3130,7 +3154,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TBD  Weekly Timetable</t>
+          <t>TBD_HS159  Weekly Timetable</t>
         </is>
       </c>
     </row>
@@ -3263,20 +3287,8 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>HS159 TUT
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>HS159 TUT
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -3377,16 +3389,16 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>NEW TUT
-(CSE_4_B)
-Room: 111</t>
+          <t>HS159 TUT
+(CSE_4_B)
+Room: 102</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>NEW TUT
-(CSE_4_B)
-Room: 111</t>
+          <t>HS159 TUT
+(CSE_4_B)
+Room: 102</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
@@ -3395,20 +3407,8 @@
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>EC155 TUT
-(CSE_4_B)
-Room: 104</t>
-        </is>
-      </c>
-      <c r="S7" s="4" t="inlineStr">
-        <is>
-          <t>EC155 TUT
-(CSE_4_B)
-Room: 104</t>
-        </is>
-      </c>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
